--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h5.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h5.xlsx
@@ -459,22 +459,22 @@
         <v>0.2750000000000057</v>
       </c>
       <c r="D2">
-        <v>0.5428599139587965</v>
+        <v>0.4545641519681511</v>
       </c>
       <c r="E2">
         <v>-0.4530390842034671</v>
       </c>
       <c r="F2">
-        <v>-0.1851791702446762</v>
+        <v>-0.2734749322353217</v>
       </c>
       <c r="G2">
-        <v>-0.2678599139587908</v>
+        <v>-0.1795641519681454</v>
       </c>
       <c r="H2">
-        <v>-0.2678599139587908</v>
+        <v>-0.1795641519681454</v>
       </c>
       <c r="I2">
-        <v>-0.1709530867234093</v>
+        <v>-0.1304558732548023</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -497,31 +497,31 @@
         <v>0.25</v>
       </c>
       <c r="D3">
-        <v>0.4719268283715035</v>
+        <v>-3.472069617300918</v>
       </c>
       <c r="E3">
         <v>-0.4480161645848688</v>
       </c>
       <c r="F3">
-        <v>-0.2260893362133653</v>
+        <v>-4.170085781885787</v>
       </c>
       <c r="G3">
-        <v>-0.2219268283715035</v>
+        <v>3.722069617300918</v>
       </c>
       <c r="H3">
-        <v>-0.2219268283715035</v>
+        <v>3.722069617300918</v>
       </c>
       <c r="I3">
-        <v>-0.1496020957799361</v>
+        <v>17.18889694455666</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -535,31 +535,31 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D4">
-        <v>0.48227310868843</v>
+        <v>0.2106334353471853</v>
       </c>
       <c r="E4">
         <v>-0.1530181086519004</v>
       </c>
       <c r="F4">
-        <v>-0.02074499996347889</v>
+        <v>-0.2923846733047236</v>
       </c>
       <c r="G4">
-        <v>-0.1322731086884215</v>
+        <v>0.1393665646528232</v>
       </c>
       <c r="H4">
-        <v>-0.1322731086884215</v>
+        <v>0.1393665646528233</v>
       </c>
       <c r="I4">
-        <v>-0.02298418655192004</v>
+        <v>0.06207425560810518</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -573,22 +573,22 @@
         <v>0.6</v>
       </c>
       <c r="D5">
-        <v>0.5067962668890756</v>
+        <v>0.3385397466524668</v>
       </c>
       <c r="E5">
         <v>0.366018718502528</v>
       </c>
       <c r="F5">
-        <v>0.2728149853916036</v>
+        <v>0.1045584651549948</v>
       </c>
       <c r="G5">
-        <v>0.09320373311092434</v>
+        <v>0.2614602533475332</v>
       </c>
       <c r="H5">
-        <v>-0.09320373311092434</v>
+        <v>-0.2614602533475332</v>
       </c>
       <c r="I5">
-        <v>-0.05954168604001192</v>
+        <v>-0.1230372296586646</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -611,25 +611,25 @@
         <v>0.5</v>
       </c>
       <c r="D6">
-        <v>0.4949878106618999</v>
+        <v>0.2805196674528365</v>
       </c>
       <c r="E6">
         <v>0.1776792908944405</v>
       </c>
       <c r="F6">
-        <v>0.1726671015563404</v>
+        <v>-0.04180104165272297</v>
       </c>
       <c r="G6">
-        <v>0.005012189338100104</v>
+        <v>0.2194803325471635</v>
       </c>
       <c r="H6">
-        <v>-0.005012189338100104</v>
+        <v>-0.1358782492417175</v>
       </c>
       <c r="I6">
-        <v>-0.00175600245288364</v>
+        <v>-0.02982260332949853</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -649,22 +649,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D7">
-        <v>0.4841164530817195</v>
+        <v>0.2200509895714168</v>
       </c>
       <c r="E7">
         <v>0.4337623012868961</v>
       </c>
       <c r="F7">
-        <v>0.4178787543686299</v>
+        <v>0.1538132908583271</v>
       </c>
       <c r="G7">
-        <v>0.01588354691826627</v>
+        <v>0.279949010428569</v>
       </c>
       <c r="H7">
-        <v>-0.01588354691826621</v>
+        <v>-0.279949010428569</v>
       </c>
       <c r="I7">
-        <v>-0.01352708066502631</v>
+        <v>-0.1644912055730357</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -687,22 +687,22 @@
         <v>0.5200000000000102</v>
       </c>
       <c r="D8">
-        <v>0.4884982359752384</v>
+        <v>0.3268879320539327</v>
       </c>
       <c r="E8">
         <v>0.2040735922691153</v>
       </c>
       <c r="F8">
-        <v>0.1725718282443434</v>
+        <v>0.01096152432303771</v>
       </c>
       <c r="G8">
-        <v>0.03150176402477184</v>
+        <v>0.1931120679460775</v>
       </c>
       <c r="H8">
-        <v>-0.03150176402477184</v>
+        <v>-0.1931120679460775</v>
       </c>
       <c r="I8">
-        <v>-0.01186499515802593</v>
+        <v>-0.04152587604613655</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -725,31 +725,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D9">
-        <v>0.4780267243467785</v>
+        <v>0.336770965865017</v>
       </c>
       <c r="E9">
         <v>0.2088650222990921</v>
       </c>
       <c r="F9">
-        <v>0.2868917466458649</v>
+        <v>0.1456359881641034</v>
       </c>
       <c r="G9">
-        <v>-0.07802672434677282</v>
+        <v>0.0632290341349887</v>
       </c>
       <c r="H9">
-        <v>0.07802672434677282</v>
+        <v>-0.0632290341349887</v>
       </c>
       <c r="I9">
-        <v>0.0386822767535149</v>
+        <v>-0.02241475649146538</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -763,22 +763,22 @@
         <v>0.4799999999999898</v>
       </c>
       <c r="D10">
-        <v>0.4795335378625585</v>
+        <v>0.3518195137012068</v>
       </c>
       <c r="E10">
         <v>-0.3441758241758278</v>
       </c>
       <c r="F10">
-        <v>-0.3446422863132591</v>
+        <v>-0.4723563104746108</v>
       </c>
       <c r="G10">
-        <v>0.0004664621374313449</v>
+        <v>0.128180486298783</v>
       </c>
       <c r="H10">
-        <v>0.0004664621374313449</v>
+        <v>0.128180486298783</v>
       </c>
       <c r="I10">
-        <v>0.0003213075681201688</v>
+        <v>0.1046634860980766</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -801,31 +801,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D11">
-        <v>0.4807179898948805</v>
+        <v>0.3941426368088483</v>
       </c>
       <c r="E11">
         <v>0.6488415319443164</v>
       </c>
       <c r="F11">
-        <v>0.6795595218392083</v>
+        <v>0.5929841687531761</v>
       </c>
       <c r="G11">
-        <v>-0.03071798989489194</v>
+        <v>0.05585736319114026</v>
       </c>
       <c r="H11">
-        <v>0.03071798989489194</v>
+        <v>-0.05585736319114032</v>
       </c>
       <c r="I11">
-        <v>0.0408058101464861</v>
+        <v>-0.06936510918395217</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,22 +839,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D12">
-        <v>0.487852489967288</v>
+        <v>0.404328163291647</v>
       </c>
       <c r="E12">
         <v>0.5746895714685679</v>
       </c>
       <c r="F12">
-        <v>0.5625420614358702</v>
+        <v>0.4790177347602291</v>
       </c>
       <c r="G12">
-        <v>0.01214751003269776</v>
+        <v>0.09567183670833879</v>
       </c>
       <c r="H12">
-        <v>-0.01214751003269776</v>
+        <v>-0.09567183670833879</v>
       </c>
       <c r="I12">
-        <v>-0.01381453267020794</v>
+        <v>-0.100810113339905</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -877,31 +877,31 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D13">
-        <v>0.4863464585416197</v>
+        <v>0.3731712274873865</v>
       </c>
       <c r="E13">
         <v>0.3648406583130818</v>
       </c>
       <c r="F13">
-        <v>0.4021871168546892</v>
+        <v>0.2890118858004561</v>
       </c>
       <c r="G13">
-        <v>-0.0373464585416074</v>
+        <v>0.07582877251262576</v>
       </c>
       <c r="H13">
-        <v>0.0373464585416074</v>
+        <v>-0.07582877251262576</v>
       </c>
       <c r="I13">
-        <v>0.02864577100556454</v>
+        <v>-0.04958083582438706</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -915,22 +915,22 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D14">
-        <v>0.4884169634587264</v>
+        <v>0.3510891542954321</v>
       </c>
       <c r="E14">
         <v>0.3220044792833222</v>
       </c>
       <c r="F14">
-        <v>0.4604214427420401</v>
+        <v>0.3230936335787457</v>
       </c>
       <c r="G14">
-        <v>-0.1384169634587179</v>
+        <v>-0.001089154295423556</v>
       </c>
       <c r="H14">
-        <v>0.1384169634587179</v>
+        <v>0.001089154295423556</v>
       </c>
       <c r="I14">
-        <v>0.1083010202581382</v>
+        <v>0.0007026113805933404</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -953,22 +953,22 @@
         <v>0.3</v>
       </c>
       <c r="D15">
-        <v>0.483937524051166</v>
+        <v>0.3205229952170769</v>
       </c>
       <c r="E15">
         <v>2.521807318894706</v>
       </c>
       <c r="F15">
-        <v>2.705744842945872</v>
+        <v>2.542330314111783</v>
       </c>
       <c r="G15">
-        <v>-0.183937524051166</v>
+        <v>-0.0205229952170769</v>
       </c>
       <c r="H15">
-        <v>0.1839375240511663</v>
+        <v>0.0205229952170769</v>
       </c>
       <c r="I15">
-        <v>0.9615430014972768</v>
+        <v>0.1039312724208106</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -991,31 +991,31 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D16">
-        <v>0.4815630880798353</v>
+        <v>0.2977430149666537</v>
       </c>
       <c r="E16">
         <v>10.04095764975201</v>
       </c>
       <c r="F16">
-        <v>10.17252073783183</v>
+        <v>9.988700664718653</v>
       </c>
       <c r="G16">
-        <v>-0.1315630880798268</v>
+        <v>0.05225698503335485</v>
       </c>
       <c r="H16">
-        <v>0.131563088079826</v>
+        <v>-0.0522569850333543</v>
       </c>
       <c r="I16">
-        <v>2.659347637505348</v>
+        <v>-1.046689554762494</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1029,22 +1029,22 @@
         <v>0.3</v>
       </c>
       <c r="D17">
-        <v>0.4819364423583523</v>
+        <v>0.3184374724902624</v>
       </c>
       <c r="E17">
         <v>-8.180304150385469</v>
       </c>
       <c r="F17">
-        <v>-7.998367708027118</v>
+        <v>-8.161866677895206</v>
       </c>
       <c r="G17">
-        <v>-0.1819364423583523</v>
+        <v>-0.0184374724902624</v>
       </c>
       <c r="H17">
-        <v>-0.1819364423583512</v>
+        <v>-0.01843747249026251</v>
       </c>
       <c r="I17">
-        <v>-2.943490000002761</v>
+        <v>-0.3013083250775992</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -1067,28 +1067,28 @@
         <v>0.3490000000000038</v>
       </c>
       <c r="D18">
-        <v>0.4770211719320328</v>
+        <v>0.2947256017300491</v>
       </c>
       <c r="E18">
         <v>0.008367396593683296</v>
       </c>
       <c r="F18">
-        <v>0.1363885685257123</v>
+        <v>-0.04590700167627143</v>
       </c>
       <c r="G18">
-        <v>-0.128021171932029</v>
+        <v>0.05427439826995473</v>
       </c>
       <c r="H18">
-        <v>0.128021171932029</v>
+        <v>0.03753960508258813</v>
       </c>
       <c r="I18">
-        <v>0.01853182829873694</v>
+        <v>0.002037439477149205</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1105,31 +1105,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D19">
-        <v>0.4744373245141269</v>
+        <v>0.2883141098898073</v>
       </c>
       <c r="E19">
         <v>2.206937868393077</v>
       </c>
       <c r="F19">
-        <v>2.281375192907199</v>
+        <v>2.095251978282879</v>
       </c>
       <c r="G19">
-        <v>-0.07443732451412122</v>
+        <v>0.1116858901101984</v>
       </c>
       <c r="H19">
-        <v>0.07443732451412144</v>
+        <v>-0.111685890110198</v>
       </c>
       <c r="I19">
-        <v>0.3340980158649787</v>
+        <v>-0.4804939024490604</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1143,22 +1143,22 @@
         <v>1.000000000000028</v>
       </c>
       <c r="D20">
-        <v>0.4729136186556157</v>
+        <v>0.2775858138434474</v>
       </c>
       <c r="E20">
         <v>-0.63309211813023</v>
       </c>
       <c r="F20">
-        <v>-1.160178499474642</v>
+        <v>-1.355506304286811</v>
       </c>
       <c r="G20">
-        <v>0.5270863813444122</v>
+        <v>0.7224141861565806</v>
       </c>
       <c r="H20">
-        <v>0.5270863813444122</v>
+        <v>0.7224141861565805</v>
       </c>
       <c r="I20">
-        <v>0.9452085206046112</v>
+        <v>1.436591710922666</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1181,22 +1181,22 @@
         <v>0.5</v>
       </c>
       <c r="D21">
-        <v>0.4533521829828927</v>
+        <v>0.1535384321437448</v>
       </c>
       <c r="E21">
         <v>-1.194266296544459</v>
       </c>
       <c r="F21">
-        <v>-1.240914113561566</v>
+        <v>-1.540727864400714</v>
       </c>
       <c r="G21">
-        <v>0.0466478170171073</v>
+        <v>0.3464615678562552</v>
       </c>
       <c r="H21">
-        <v>0.04664781701710741</v>
+        <v>0.3464615678562553</v>
       </c>
       <c r="I21">
-        <v>0.1135958501742704</v>
+        <v>0.9475703650787679</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -1219,31 +1219,31 @@
         <v>0.392417277716504</v>
       </c>
       <c r="D22">
-        <v>0.3231029861182279</v>
+        <v>-2.351595956105766</v>
       </c>
       <c r="E22">
         <v>0.7396069183282994</v>
       </c>
       <c r="F22">
-        <v>0.6702926267300233</v>
+        <v>-2.004406315493971</v>
       </c>
       <c r="G22">
-        <v>0.06931429159827607</v>
+        <v>2.74401323382227</v>
       </c>
       <c r="H22">
-        <v>-0.06931429159827607</v>
+        <v>1.264799397165671</v>
       </c>
       <c r="I22">
-        <v>-0.09772618819044943</v>
+        <v>3.470626283953032</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1257,31 +1257,31 @@
         <v>0.4639324016758237</v>
       </c>
       <c r="D23">
-        <v>0.4557767256476296</v>
+        <v>0.4798981714231107</v>
       </c>
       <c r="E23">
         <v>0.2285275052539781</v>
       </c>
       <c r="F23">
-        <v>0.220371829225784</v>
+        <v>0.2444932750012651</v>
       </c>
       <c r="G23">
-        <v>0.008155676028194114</v>
+        <v>-0.01596576974728697</v>
       </c>
       <c r="H23">
-        <v>-0.008155676028194114</v>
+        <v>0.01596576974728697</v>
       </c>
       <c r="I23">
-        <v>-0.003661077541288887</v>
+        <v>0.007552140863237244</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1295,22 +1295,22 @@
         <v>0.45723</v>
       </c>
       <c r="D24">
-        <v>0.4523838324772173</v>
+        <v>0.2378799164465338</v>
       </c>
       <c r="E24">
         <v>0.3175001443875122</v>
       </c>
       <c r="F24">
-        <v>0.3126539768647295</v>
+        <v>0.09815006083404601</v>
       </c>
       <c r="G24">
-        <v>0.004846167522782718</v>
+        <v>0.2193500835534662</v>
       </c>
       <c r="H24">
-        <v>-0.004846167522782718</v>
+        <v>-0.2193500835534662</v>
       </c>
       <c r="I24">
-        <v>-0.003053832436760287</v>
+        <v>-0.09117290724436418</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -1333,28 +1333,28 @@
         <v>0.4306032481654398</v>
       </c>
       <c r="D25">
-        <v>0.4457871044344521</v>
+        <v>0.2876762559939251</v>
       </c>
       <c r="E25">
         <v>0.03045435555422921</v>
       </c>
       <c r="F25">
-        <v>0.04563821182324146</v>
+        <v>-0.1124726366172855</v>
       </c>
       <c r="G25">
-        <v>-0.01518385626901225</v>
+        <v>0.1429269921715147</v>
       </c>
       <c r="H25">
-        <v>0.01518385626901225</v>
+        <v>0.08201828106305631</v>
       </c>
       <c r="I25">
-        <v>0.001155378606199645</v>
+        <v>0.01172262621542054</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
@@ -1371,22 +1371,22 @@
         <v>0.49</v>
       </c>
       <c r="D26">
-        <v>0.4533258918405827</v>
+        <v>0.3599362862932105</v>
       </c>
       <c r="E26">
         <v>0.9253061035472806</v>
       </c>
       <c r="F26">
-        <v>0.8886319953878633</v>
+        <v>0.7952423898404911</v>
       </c>
       <c r="G26">
-        <v>0.0366741081594173</v>
+        <v>0.1300637137067895</v>
       </c>
       <c r="H26">
-        <v>-0.0366741081594173</v>
+        <v>-0.1300637137067895</v>
       </c>
       <c r="I26">
-        <v>-0.06652456203483526</v>
+        <v>-0.2237809266626352</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -1409,22 +1409,22 @@
         <v>0.53</v>
       </c>
       <c r="D27">
-        <v>0.461224295770041</v>
+        <v>0.4472171537802698</v>
       </c>
       <c r="E27">
         <v>0.8652267436446591</v>
       </c>
       <c r="F27">
-        <v>0.7964510394147001</v>
+        <v>0.7824438974249289</v>
       </c>
       <c r="G27">
-        <v>0.06877570422995904</v>
+        <v>0.0827828462197302</v>
       </c>
       <c r="H27">
-        <v>-0.06877570422995904</v>
+        <v>-0.0827828462197302</v>
       </c>
       <c r="I27">
-        <v>-0.1142830597331845</v>
+        <v>-0.136398865300428</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
@@ -1447,22 +1447,22 @@
         <v>0.7368271734067955</v>
       </c>
       <c r="D28">
-        <v>0.4603037815877094</v>
+        <v>0.3934798787210216</v>
       </c>
       <c r="E28">
         <v>0.7182674109717584</v>
       </c>
       <c r="F28">
-        <v>0.4417440191526723</v>
+        <v>0.3749201162859844</v>
       </c>
       <c r="G28">
-        <v>0.2765233918190861</v>
+        <v>0.3433472946857739</v>
       </c>
       <c r="H28">
-        <v>-0.2765233918190861</v>
+        <v>-0.343347294685774</v>
       </c>
       <c r="I28">
-        <v>-0.3207702952069164</v>
+        <v>-0.3753429800681768</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,22 +1485,22 @@
         <v>0.617601205077456</v>
       </c>
       <c r="D29">
-        <v>0.4591770745730561</v>
+        <v>0.3769007839823598</v>
       </c>
       <c r="E29">
         <v>0.7472188330748641</v>
       </c>
       <c r="F29">
-        <v>0.5887947025704643</v>
+        <v>0.506518411979768</v>
       </c>
       <c r="G29">
-        <v>0.1584241305043999</v>
+        <v>0.2407004210950962</v>
       </c>
       <c r="H29">
-        <v>-0.1584241305043999</v>
+        <v>-0.2407004210950962</v>
       </c>
       <c r="I29">
-        <v>-0.2116567827267202</v>
+        <v>-0.3017750828272557</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -1523,22 +1523,22 @@
         <v>0.48</v>
       </c>
       <c r="D30">
-        <v>0.4609314551376181</v>
+        <v>0.3677812325286816</v>
       </c>
       <c r="E30">
         <v>0.7670636170015632</v>
       </c>
       <c r="F30">
-        <v>0.7479950721391813</v>
+        <v>0.6548448495302448</v>
       </c>
       <c r="G30">
-        <v>0.01906854486238191</v>
+        <v>0.1122187674713184</v>
       </c>
       <c r="H30">
-        <v>-0.01906854486238196</v>
+        <v>-0.1122187674713184</v>
       </c>
       <c r="I30">
-        <v>-0.02888996458302195</v>
+        <v>-0.159564815571232</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
@@ -1561,31 +1561,31 @@
         <v>0.4192972035713893</v>
       </c>
       <c r="D31">
-        <v>0.4604031385793151</v>
+        <v>0.3529487950840318</v>
       </c>
       <c r="E31">
         <v>0.2057013640468817</v>
       </c>
       <c r="F31">
-        <v>0.2468072990548075</v>
+        <v>0.1393529555595242</v>
       </c>
       <c r="G31">
-        <v>-0.04110593500792581</v>
+        <v>0.06634840848735746</v>
       </c>
       <c r="H31">
-        <v>0.04110593500792581</v>
+        <v>-0.06634840848735746</v>
       </c>
       <c r="I31">
-        <v>0.01860079169598143</v>
+        <v>-0.02289380494757301</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1599,31 +1599,31 @@
         <v>0.4257107569248291</v>
       </c>
       <c r="D32">
-        <v>0.456980808927669</v>
+        <v>0.3016504016882561</v>
       </c>
       <c r="E32">
         <v>0.4924727979357907</v>
       </c>
       <c r="F32">
-        <v>0.5237428499386305</v>
+        <v>0.3684124426992176</v>
       </c>
       <c r="G32">
-        <v>-0.03127005200283989</v>
+        <v>0.124060355236573</v>
       </c>
       <c r="H32">
-        <v>0.03127005200283983</v>
+        <v>-0.124060355236573</v>
       </c>
       <c r="I32">
-        <v>0.03177711615513273</v>
+        <v>-0.1068017287711018</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1637,31 +1637,31 @@
         <v>0.33</v>
       </c>
       <c r="D33">
-        <v>0.4528114806763079</v>
+        <v>0.2575889808286466</v>
       </c>
       <c r="E33">
         <v>0.2247871831659499</v>
       </c>
       <c r="F33">
-        <v>0.3475986638422578</v>
+        <v>0.1523761639945965</v>
       </c>
       <c r="G33">
-        <v>-0.1228114806763079</v>
+        <v>0.0724110191713534</v>
       </c>
       <c r="H33">
-        <v>0.1228114806763079</v>
+        <v>-0.0724110191713534</v>
       </c>
       <c r="I33">
-        <v>0.07029555338924062</v>
+        <v>-0.02731078236197415</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1675,31 +1675,31 @@
         <v>0.3806835540682556</v>
       </c>
       <c r="D34">
-        <v>0.4534508657353486</v>
+        <v>0.2737413731481941</v>
       </c>
       <c r="E34">
         <v>0.5813332769805371</v>
       </c>
       <c r="F34">
-        <v>0.65410058864763</v>
+        <v>0.4743910960604755</v>
       </c>
       <c r="G34">
-        <v>-0.07276731166709299</v>
+        <v>0.1069421809200615</v>
       </c>
       <c r="H34">
-        <v>0.07276731166709294</v>
+        <v>-0.1069421809200616</v>
       </c>
       <c r="I34">
-        <v>0.08989920114424627</v>
+        <v>-0.1129014669034705</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1713,28 +1713,28 @@
         <v>0.3995464824356247</v>
       </c>
       <c r="D35">
-        <v>0.4517556824517064</v>
+        <v>0.2550055084590223</v>
       </c>
       <c r="E35">
         <v>-0.01213374733938011</v>
       </c>
       <c r="F35">
-        <v>0.0400754526767016</v>
+        <v>-0.1566747213159825</v>
       </c>
       <c r="G35">
-        <v>-0.0522092000160817</v>
+        <v>0.1445409739766024</v>
       </c>
       <c r="H35">
-        <v>0.02794170533732149</v>
+        <v>0.1445409739766024</v>
       </c>
       <c r="I35">
-        <v>0.001458814082746635</v>
+        <v>0.02439974047494486</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -1751,31 +1751,31 @@
         <v>0.3505327396020164</v>
       </c>
       <c r="D36">
-        <v>0.4489165116824054</v>
+        <v>0.2440474222454754</v>
       </c>
       <c r="E36">
         <v>0.6272238950261231</v>
       </c>
       <c r="F36">
-        <v>0.7256076671065121</v>
+        <v>0.5207385776695821</v>
       </c>
       <c r="G36">
-        <v>-0.09838377208038895</v>
+        <v>0.106485317356541</v>
       </c>
       <c r="H36">
-        <v>0.09838377208038906</v>
+        <v>-0.106485317356541</v>
       </c>
       <c r="I36">
-        <v>0.1330966720720139</v>
+        <v>-0.1222411482184017</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1789,31 +1789,31 @@
         <v>0.32</v>
       </c>
       <c r="D37">
-        <v>0.4475575600334996</v>
+        <v>0.2534447081011285</v>
       </c>
       <c r="E37">
         <v>0.32</v>
       </c>
       <c r="F37">
-        <v>0.4475575600334996</v>
+        <v>0.2534447081011285</v>
       </c>
       <c r="G37">
-        <v>-0.1275575600334996</v>
+        <v>0.06655529189887149</v>
       </c>
       <c r="H37">
-        <v>0.1275575600334996</v>
+        <v>-0.06655529189887149</v>
       </c>
       <c r="I37">
-        <v>0.09790776954313961</v>
+        <v>-0.03816577993553377</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
